--- a/test_multi.xlsx
+++ b/test_multi.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emilio.cornejo\Desktop\fantasy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA4E00E-C0AB-4972-B5ED-82AD2409CFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07FC4D6-23EA-4DE7-86B3-846B7412B7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{23D2E913-A0C1-4AB9-9120-D8F79DF3DCE7}"/>
   </bookViews>
   <sheets>
     <sheet name="multiplier" sheetId="1" r:id="rId1"/>
-    <sheet name="Teams backup" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
-  <si>
-    <t>fut</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>legacy</t>
   </si>
@@ -49,45 +45,6 @@
     <t>b8</t>
   </si>
   <si>
-    <t>nrg</t>
-  </si>
-  <si>
-    <t>eyeballers</t>
-  </si>
-  <si>
-    <t>bc</t>
-  </si>
-  <si>
-    <t>mibr</t>
-  </si>
-  <si>
-    <t>fokus</t>
-  </si>
-  <si>
-    <t>pari</t>
-  </si>
-  <si>
-    <t>mongol</t>
-  </si>
-  <si>
-    <t>asstralis</t>
-  </si>
-  <si>
-    <t>3Dmax</t>
-  </si>
-  <si>
-    <t>eye</t>
-  </si>
-  <si>
-    <t>voca</t>
-  </si>
-  <si>
-    <t>inner</t>
-  </si>
-  <si>
-    <t>wildcard</t>
-  </si>
-  <si>
     <t>valve points</t>
   </si>
   <si>
@@ -97,22 +54,46 @@
     <t>average points</t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Parivision</t>
-  </si>
-  <si>
-    <t>The mongolz</t>
-  </si>
-  <si>
-    <t>astralis</t>
-  </si>
-  <si>
-    <t>bc.game</t>
-  </si>
-  <si>
-    <t>innerCircle</t>
+    <t>vitality</t>
+  </si>
+  <si>
+    <t>navi</t>
+  </si>
+  <si>
+    <t>furia</t>
+  </si>
+  <si>
+    <t>falcons</t>
+  </si>
+  <si>
+    <t>aurora</t>
+  </si>
+  <si>
+    <t>mouz</t>
+  </si>
+  <si>
+    <t>spirit</t>
+  </si>
+  <si>
+    <t>g2</t>
+  </si>
+  <si>
+    <t>3dmax</t>
+  </si>
+  <si>
+    <t>liquid</t>
+  </si>
+  <si>
+    <t>pua</t>
+  </si>
+  <si>
+    <t>m8</t>
+  </si>
+  <si>
+    <t>hotu</t>
+  </si>
+  <si>
+    <t>rad</t>
   </si>
 </sst>
 </file>
@@ -464,296 +445,218 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A98DA87-3222-44A7-A23E-C6CB86F62CE1}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>1800</v>
+        <v>2080</v>
       </c>
       <c r="C2">
         <f>B2/F2</f>
-        <v>1.1847821317302207</v>
+        <v>1.2783774440133677</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <f>AVERAGEA(B2:B16)</f>
-        <v>1519.2666666666667</v>
+        <f>AVERAGEA(B2:B17)</f>
+        <v>1627.0625</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>1817</v>
+        <v>1931</v>
       </c>
       <c r="C3">
         <f>B3/F2</f>
-        <v>1.1959717407521173</v>
+        <v>1.1868013674951023</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C4">
         <f>B4/F2</f>
-        <v>1.1907060423888718</v>
+        <v>1.1112050090270043</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>1748</v>
+        <v>1777</v>
       </c>
       <c r="C5">
         <f>B5/F2</f>
-        <v>1.1505550923691255</v>
+        <v>1.0921522682748819</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>1586</v>
+        <v>1810</v>
       </c>
       <c r="C6">
         <f>B6/F2</f>
-        <v>1.0439247005134056</v>
+        <v>1.1124342181077862</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>1571</v>
+        <v>1796</v>
       </c>
       <c r="C7">
         <f>B7/F2</f>
-        <v>1.0340515160823205</v>
+        <v>1.1038297545423117</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>1589</v>
+        <v>1737</v>
       </c>
       <c r="C8">
         <f>B8/F2</f>
-        <v>1.0458993373996226</v>
+        <v>1.0675680866592403</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>1416</v>
+        <v>1678</v>
       </c>
       <c r="C9">
         <f>B9/F2</f>
-        <v>0.93202861029444029</v>
+        <v>1.0313064187761687</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B10">
-        <v>1466</v>
+        <v>1586</v>
       </c>
       <c r="C10">
         <f>B10/F2</f>
-        <v>0.96493922506472418</v>
+        <v>0.97476280106019286</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B11">
-        <v>1236</v>
+        <v>1571</v>
       </c>
       <c r="C11">
         <f>B11/F2</f>
-        <v>0.81355039712141819</v>
+        <v>0.96554373295432716</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B12">
-        <v>1496</v>
+        <v>1589</v>
       </c>
       <c r="C12">
         <f>B12/F2</f>
-        <v>0.98468559392689459</v>
+        <v>0.976606614681366</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>1420</v>
+        <v>1373</v>
       </c>
       <c r="C13">
         <f>B13/F2</f>
-        <v>0.93466145947606305</v>
+        <v>0.84385203395690089</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="C14">
         <f>B14/F2</f>
-        <v>0.87213129141252355</v>
+        <v>0.8223408750432144</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>1265</v>
+        <v>1391</v>
       </c>
       <c r="C15">
         <f>B15/F2</f>
-        <v>0.83263855368818296</v>
+        <v>0.85491491568393962</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16">
-        <v>1245</v>
+        <v>1319</v>
       </c>
       <c r="C16">
         <f>B16/F2</f>
-        <v>0.81947430778006936</v>
+        <v>0.81066338877578459</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>1249</v>
+      </c>
+      <c r="C17">
+        <f>B17/F2</f>
+        <v>0.76764107094841161</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67AC667-8315-4B42-B8FC-8DCB97DF0855}">
-  <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/test_multi.xlsx
+++ b/test_multi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emilio.cornejo\Desktop\fantasy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07FC4D6-23EA-4DE7-86B3-846B7412B7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0CE4CF-2F2E-4E6F-92D3-F6D95893AE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{23D2E913-A0C1-4AB9-9120-D8F79DF3DCE7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{23D2E913-A0C1-4AB9-9120-D8F79DF3DCE7}"/>
   </bookViews>
   <sheets>
     <sheet name="multiplier" sheetId="1" r:id="rId1"/>
